--- a/sources/pfd.xlsx
+++ b/sources/pfd.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILLING</t>
+          <t>FIM SAG MILLING</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL RECYCLE CRUSHING</t>
+          <t>FIM SAG MILL RECYCLE CRUSHING</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL AREA WASHDOWN PUMP</t>
+          <t>FIM SAG MILL AREA WASHDOWN PUMP</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL FEED CONVEYOR</t>
+          <t>FIM SAG MILL FEED CONVEYOR</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL</t>
+          <t>FIM SAG MILL</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL TRANSFER HOPPER</t>
+          <t>FIM SAG MILL TRANSFER HOPPER</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FIMISTON MILL TRANSFER PUMP 1</t>
+          <t>FIM MILL TRANSFER PUMP 1</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FIMISTON MILL TRANSFER PUMP 2</t>
+          <t>FIM MILL TRANSFER PUMP 2</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL RECYCLE CRUSHING SCREEN</t>
+          <t>FIM SAG MILL RECYCLE CRUSHING SCREEN</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FIMISTON CONCENTRATE THICKENER (EXISTING)</t>
+          <t>FIM CONCENTRATE THICKENER (EXISTING)</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FIMISTON CONCENTRATE THICKENER U/F PUMP 1</t>
+          <t>FIM CONCENTRATE THICKENER U/F PUMP 1</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>FIMISTON CONCENTRATE THICKENER U/F PUMP 2</t>
+          <t>FIM CONCENTRATE THICKENER U/F PUMP 2</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL FEED CONVEYOR</t>
+          <t>FIM SAG MILL FEED CONVEYOR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL DISCHARGE</t>
+          <t>FIM SAG MILL DISCHARGE</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FIMISTON SAG MILL DISCHARGE</t>
+          <t>FIM SAG MILL DISCHARGE</t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAG MILL DISCHARGE FIMISTON MILL TRANSFER PUMP 2</t>
+          <t>SAG MILL DISCHARGE FIM MILL TRANSFER PUMP 2</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FIMISTON MILL TRANSFER PUMP 2</t>
+          <t>FIM MILL TRANSFER PUMP 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SCHEME WATER FIMISTON MILL TRANSFER PUMP 1</t>
+          <t>SCHEME WATER FIM MILL TRANSFER PUMP 1</t>
         </is>
       </c>
     </row>
@@ -18666,7 +18666,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>FILTRATE FIMISTON</t>
+          <t>FILTRATE FIM</t>
         </is>
       </c>
     </row>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FIMISTON SAG CIRCUIT</t>
+          <t>FIM SAG CIRCUIT</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>FILTRATE FIMISTON</t>
+          <t>FILTRATE FIM</t>
         </is>
       </c>
     </row>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>GIDJI</t>
+          <t>OFFSITE ROASTER</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>LOADED CARBON GIDJI</t>
+          <t>LOADED CARBON OFFSITE ROASTER</t>
         </is>
       </c>
     </row>
@@ -24911,7 +24911,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>SPILLAGE FIMISTON CONCENTRATE</t>
+          <t>SPILLAGE FIM CONCENTRATE</t>
         </is>
       </c>
     </row>
